--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1373053-9-CM26</t>
+          <t>846677-2-SE26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -789,22 +789,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.979.950-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Superintendencia del Medio Ambiente</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9583.110000000001</v>
+        <v>104140.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3378-4239-CM26</t>
+          <t>1373053-9-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>16186.82</v>
+        <v>9583.110000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2701-560-CM26</t>
+          <t>3378-4239-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7874.28</v>
+        <v>16186.82</v>
       </c>
     </row>
     <row r="9">
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>550716-10-CM26</t>
+          <t>2701-560-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7128.25</v>
+        <v>7874.28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>307-82-CM26</t>
+          <t>550716-10-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>699.64</v>
+        <v>7128.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>670784-10-CM26</t>
+          <t>307-82-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,22 +1179,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10292.87</v>
+        <v>699.64</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1477-270-CM26</t>
+          <t>670784-10-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>37103.35</v>
+        <v>10292.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>606591-7-CM26</t>
+          <t>1477-270-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>31368.75</v>
+        <v>37103.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1186801-8-CM26</t>
+          <t>606591-7-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1374,22 +1374,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1201.42</v>
+        <v>31368.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>1186801-8-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1483,71 +1483,136 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>37448.52</v>
+        <v>1201.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>544143-9-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>37448.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>1373053-10-CM26</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>ago-2026</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>82.174.900-k</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Tarapacá</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n">
+      <c r="M18" s="2" t="n">
         <v>9602.950000000001</v>
       </c>
     </row>
